--- a/TPE_23P039_N_2.xlsx
+++ b/TPE_23P039_N_2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Armand\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Armand\Desktop\ABANA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E1BEED5-2BF0-4F88-B8BA-CB031D142AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B784D45-4597-442D-A11E-621F75102E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="87">
   <si>
     <t>Informatique</t>
   </si>
@@ -156,10 +156,6 @@
     <t>Magasinier</t>
   </si>
   <si>
-    <t>Responsable
-du stock</t>
-  </si>
-  <si>
     <t>ERP
 (module stock)</t>
   </si>
@@ -224,10 +220,6 @@
   <si>
     <t>Opérateur
 machine</t>
-  </si>
-  <si>
-    <t>Opérateur
-de production</t>
   </si>
   <si>
     <t>Capteurs /
@@ -433,6 +425,21 @@
 Poste de
 travail
 concerné</t>
+  </si>
+  <si>
+    <t>Jean</t>
+  </si>
+  <si>
+    <t>Gabriel</t>
+  </si>
+  <si>
+    <t>Pierre</t>
+  </si>
+  <si>
+    <t>Helena</t>
+  </si>
+  <si>
+    <t>Lara</t>
   </si>
 </sst>
 </file>
@@ -540,24 +547,20 @@
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -569,6 +572,10 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -890,74 +897,74 @@
     <col min="16" max="16" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="9" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:16" s="7" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+    </row>
+    <row r="2" spans="1:16" s="9" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-    </row>
-    <row r="2" spans="1:16" s="11" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P2" s="10" t="s">
-        <v>68</v>
+      <c r="P2" s="8" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:16" s="3" customFormat="1" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -974,7 +981,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>4</v>
@@ -1003,7 +1010,7 @@
       <c r="N3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="12" t="s">
+      <c r="O3" s="10" t="s">
         <v>13</v>
       </c>
       <c r="P3" s="2" t="s">
@@ -1024,7 +1031,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>15</v>
@@ -1053,7 +1060,7 @@
       <c r="N4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="O4" s="13" t="s">
+      <c r="O4" s="11" t="s">
         <v>13</v>
       </c>
       <c r="P4" s="5" t="s">
@@ -1074,40 +1081,40 @@
         <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="N5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="O5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="O5" s="12" t="s">
+      <c r="P5" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:16" s="6" customFormat="1" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1115,49 +1122,49 @@
         <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="I6" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="J6" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="K6" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="L6" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="M6" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="L6" s="5" t="s">
+      <c r="N6" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="M6" s="5" t="s">
+      <c r="O6" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="P6" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="O6" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="3" customFormat="1" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1165,49 +1172,49 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="E7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="O7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="P7" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="O7" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
